--- a/SPC26S1 - 00 Master.xlsx
+++ b/SPC26S1 - 00 Master.xlsx
@@ -3504,7 +3504,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="23">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3655,6 +3655,62 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9F9F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4A0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBFBFBF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11696,7 +11752,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -11853,7 +11909,127 @@
         <v>25</v>
       </c>
     </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row colours by Claim Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="45" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each claim row is shaded by its Claim Status (column A) using conditional formatting, so the colour follows the status automatically when it is changed. Rows with no Claim Status keep their normal formatting. The deadline countdown columns keep their own colour bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAID - green</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Finalized - blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Received - lavender</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pending - yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Under Review - orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied - red</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Rejected - pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Not found - grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any other status is left unshaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A37">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39">
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40">
+    <cfRule type="expression" dxfId="18" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="19" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="expression" dxfId="20" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="expression" dxfId="21" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="22" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -69486,6 +69662,32 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AO1000">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/SPC26S1 - 00 Master.xlsx
+++ b/SPC26S1 - 00 Master.xlsx
@@ -4345,8 +4345,12 @@
           <cell r="K8"/>
         </row>
         <row r="9">
-          <cell r="A9"/>
-          <cell r="B9"/>
+          <cell r="A9" t="str">
+            <v>Under Review</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Waiting for account to get activated again</v>
+          </cell>
           <cell r="C9">
             <v>46111</v>
           </cell>
@@ -66134,11 +66138,11 @@
     <row r="450" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B450" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$B$2:$B$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$B$2:$B$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))),"")</f>
-        <v/>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C450" s="6">
         <f>IFERROR(IF(INDEX([1]ORTHO!$C$2:$C$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$C$2:$C$10,MATCH($D450,[1]ORTHO!$D$2:$D$10,0))),"")</f>
